--- a/demo/정보부_업무관리_데모시트.xlsx
+++ b/demo/정보부_업무관리_데모시트.xlsx
@@ -20,10 +20,10 @@
     <sheet sheetId="14" name="보유_태블릿" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="보유_태블릿보관함" state="visible" r:id="rId18"/>
     <sheet sheetId="16" name="보유_기타" state="visible" r:id="rId19"/>
-    <sheet sheetId="17" name="전자기기_개별_노트북" state="visible" r:id="rId20"/>
-    <sheet sheetId="18" name="전자기기_개별_태블릿" state="visible" r:id="rId21"/>
-    <sheet sheetId="19" name="전자기기_개별_태블릿보관함" state="visible" r:id="rId22"/>
-    <sheet sheetId="20" name="전자기기_개별_데스크톱" state="visible" r:id="rId23"/>
+    <sheet sheetId="17" name="전자기기_개별_데스크톱" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="전자기기_개별_노트북" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="전자기기_개별_태블릿" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="전자기기_개별_태블릿보관함" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="보유현황_제출본" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="대여" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="메뉴얼" state="visible" r:id="rId26"/>
@@ -611,7 +611,7 @@
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>보유_노트북 탭의 ID (예: dv-021). 물품 분류명이 "노트북" 인 묶음만 적을 수 있다</t>
+          <t>보유_데스크톱 탭의 ID (예: dv-021). 물품 분류명이 "데스크톱" 인 묶음만 적을 수 있다</t>
         </r>
       </text>
     </comment>
@@ -672,7 +672,7 @@
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>보유_태블릿 탭의 ID (예: dv-021). 물품 분류명이 "태블릿" 인 묶음만 적을 수 있다</t>
+          <t>보유_노트북 탭의 ID (예: dv-021). 물품 분류명이 "노트북" 인 묶음만 적을 수 있다</t>
         </r>
       </text>
     </comment>
@@ -733,7 +733,7 @@
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>보유_태블릿보관함 탭의 ID (예: dv-021). 물품 분류명이 "태블릿보관함" 인 묶음만 적을 수 있다</t>
+          <t>보유_태블릿 탭의 ID (예: dv-021). 물품 분류명이 "태블릿" 인 묶음만 적을 수 있다</t>
         </r>
       </text>
     </comment>
@@ -818,7 +818,7 @@
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>보유_데스크톱 탭의 ID (예: dv-021). 물품 분류명이 "데스크톱" 인 묶음만 적을 수 있다</t>
+          <t>보유_태블릿보관함 탭의 ID (예: dv-021). 물품 분류명이 "태블릿보관함" 인 묶음만 적을 수 있다</t>
         </r>
       </text>
     </comment>
@@ -1266,7 +1266,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3336" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3362" uniqueCount="1734">
   <si>
     <t>정보부 업무 관리 시스템 — 데이터 시트</t>
   </si>
@@ -1382,6 +1382,12 @@
     <t>전자기기 보유 묶음 — 기타</t>
   </si>
   <si>
+    <t>전자기기_개별_데스크톱</t>
+  </si>
+  <si>
+    <t>전자기기 개별 장비 — 데스크톱</t>
+  </si>
+  <si>
     <t>전자기기_개별_노트북</t>
   </si>
   <si>
@@ -1400,12 +1406,6 @@
     <t>전자기기 개별 장비 — 태블릿보관함</t>
   </si>
   <si>
-    <t>전자기기_개별_데스크톱</t>
-  </si>
-  <si>
-    <t>전자기기 개별 장비 — 데스크톱</t>
-  </si>
-  <si>
     <t>보유현황_제출본</t>
   </si>
   <si>
@@ -5220,6 +5220,12 @@
   </si>
   <si>
     <t>시리얼번호</t>
+  </si>
+  <si>
+    <t>물품구분</t>
+  </si>
+  <si>
+    <t>물품명</t>
   </si>
   <si>
     <t>lt-001</t>
@@ -6272,16 +6278,28 @@
     <t>lk-sheet-19</t>
   </si>
   <si>
+    <t>sheet:전자기기_개별_데스크톱</t>
+  </si>
+  <si>
+    <t>전자기기_개별_데스크톱 시트</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=18</t>
+  </si>
+  <si>
+    <t>lk-sheet-20</t>
+  </si>
+  <si>
     <t>sheet:전자기기_개별_노트북</t>
   </si>
   <si>
     <t>전자기기_개별_노트북 시트</t>
   </si>
   <si>
-    <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=18</t>
-  </si>
-  <si>
-    <t>lk-sheet-20</t>
+    <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=19</t>
+  </si>
+  <si>
+    <t>lk-sheet-21</t>
   </si>
   <si>
     <t>sheet:전자기기_개별_태블릿</t>
@@ -6290,28 +6308,16 @@
     <t>전자기기_개별_태블릿 시트</t>
   </si>
   <si>
-    <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=19</t>
-  </si>
-  <si>
-    <t>lk-sheet-21</t>
+    <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=20</t>
+  </si>
+  <si>
+    <t>lk-sheet-22</t>
   </si>
   <si>
     <t>sheet:전자기기_개별_태블릿보관함</t>
   </si>
   <si>
     <t>전자기기_개별_태블릿보관함 시트</t>
-  </si>
-  <si>
-    <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=20</t>
-  </si>
-  <si>
-    <t>lk-sheet-22</t>
-  </si>
-  <si>
-    <t>sheet:전자기기_개별_데스크톱</t>
-  </si>
-  <si>
-    <t>전자기기_개별_데스크톱 시트</t>
   </si>
   <si>
     <t>https://docs.google.com/spreadsheets/d/DEMO_SHEET_ID_REPLACE_ME/edit#gid=21</t>
@@ -7309,10 +7315,10 @@
     <hyperlink ref="A20" r:id="rId13" location="#'보유_태블릿'!A1"/>
     <hyperlink ref="A21" r:id="rId14" location="#'보유_태블릿보관함'!A1"/>
     <hyperlink ref="A22" r:id="rId15" location="#'보유_기타'!A1"/>
-    <hyperlink ref="A23" r:id="rId16" location="#'전자기기_개별_노트북'!A1"/>
-    <hyperlink ref="A24" r:id="rId17" location="#'전자기기_개별_태블릿'!A1"/>
-    <hyperlink ref="A25" r:id="rId18" location="#'전자기기_개별_태블릿보관함'!A1"/>
-    <hyperlink ref="A26" r:id="rId19" location="#'전자기기_개별_데스크톱'!A1"/>
+    <hyperlink ref="A23" r:id="rId16" location="#'전자기기_개별_데스크톱'!A1"/>
+    <hyperlink ref="A24" r:id="rId17" location="#'전자기기_개별_노트북'!A1"/>
+    <hyperlink ref="A25" r:id="rId18" location="#'전자기기_개별_태블릿'!A1"/>
+    <hyperlink ref="A26" r:id="rId19" location="#'전자기기_개별_태블릿보관함'!A1"/>
     <hyperlink ref="A27" r:id="rId20" location="#'보유현황_제출본'!A1"/>
     <hyperlink ref="A29" r:id="rId21" location="#'대여'!A1"/>
     <hyperlink ref="A30" r:id="rId22" location="#'메뉴얼'!A1"/>
@@ -10570,7 +10576,7 @@
   <sheetPr>
     <tabColor rgb="FFFA7B17"/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -10614,462 +10620,6 @@
       </c>
       <c r="L1" s="9" t="s">
         <v>1317</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>1320</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>1321</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>1326</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>1327</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>1329</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>1332</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>1334</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>1256</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>1335</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>1336</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>1210</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>1338</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>1339</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>1343</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>1219</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>1346</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>1219</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>1348</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>1350</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>1351</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>1352</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>1355</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>1249</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>1356</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>1357</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>1358</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>1360</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>1361</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>1249</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>1211</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>1356</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>1362</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>1364</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>1365</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>1356</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>1366</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>1369</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>1221</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>1206</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>1322</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>1371</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11085,15 +10635,16 @@
   <sheetPr>
     <tabColor rgb="FFFA7B17"/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>70</v>
       </c>
@@ -11130,9 +10681,543 @@
       <c r="L1" s="9" t="s">
         <v>1317</v>
       </c>
+      <c r="M1" s="9" t="s">
+        <v>1318</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>1340</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>1341</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>1353</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>1359</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>1363</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>1249</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>1358</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>1368</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>1324</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>1373</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
@@ -11934,75 +12019,75 @@
         <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="W1" s="9" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B2" s="10">
         <v>2025</v>
@@ -12011,7 +12096,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
@@ -12065,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W2" s="10" t="s">
         <v>105</v>
@@ -12073,7 +12158,7 @@
     </row>
     <row r="3" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="B3" s="10">
         <v>2025</v>
@@ -12082,7 +12167,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="E3" s="10">
         <v>0</v>
@@ -12136,7 +12221,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W3" s="10" t="s">
         <v>105</v>
@@ -12144,7 +12229,7 @@
     </row>
     <row r="4" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B4" s="10">
         <v>2025</v>
@@ -12153,7 +12238,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="E4" s="10">
         <v>0</v>
@@ -12207,7 +12292,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W4" s="10" t="s">
         <v>105</v>
@@ -12215,7 +12300,7 @@
     </row>
     <row r="5" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="B5" s="10">
         <v>2025</v>
@@ -12224,7 +12309,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="E5" s="10">
         <v>0</v>
@@ -12278,7 +12363,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W5" s="10" t="s">
         <v>105</v>
@@ -12286,7 +12371,7 @@
     </row>
     <row r="6" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="B6" s="10">
         <v>2025</v>
@@ -12295,7 +12380,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="E6" s="10">
         <v>0</v>
@@ -12349,7 +12434,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W6" s="10" t="s">
         <v>105</v>
@@ -12357,7 +12442,7 @@
     </row>
     <row r="7" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="B7" s="10">
         <v>2025</v>
@@ -12366,7 +12451,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="E7" s="10">
         <v>0</v>
@@ -12420,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W7" s="10" t="s">
         <v>105</v>
@@ -12428,7 +12513,7 @@
     </row>
     <row r="8" spans="1:23" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="B8" s="10">
         <v>2025</v>
@@ -12437,7 +12522,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="E8" s="10">
         <v>0</v>
@@ -12491,7 +12576,7 @@
         <v>16</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="W8" s="10" t="s">
         <v>105</v>
@@ -12527,31 +12612,31 @@
         <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>1189</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>1199</v>
@@ -12559,7 +12644,7 @@
     </row>
     <row r="2" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1278</v>
@@ -12580,7 +12665,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>1</v>
@@ -12589,12 +12674,12 @@
         <v>105</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>1278</v>
@@ -12609,16 +12694,16 @@
         <v>1228</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>110</v>
@@ -12629,7 +12714,7 @@
     </row>
     <row r="4" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>1278</v>
@@ -12650,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>1</v>
@@ -12664,7 +12749,7 @@
     </row>
     <row r="5" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>1278</v>
@@ -12685,21 +12770,21 @@
         <v>1</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>1236</v>
@@ -12720,21 +12805,21 @@
         <v>1</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>105</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>1236</v>
@@ -12755,7 +12840,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>1</v>
@@ -12769,7 +12854,7 @@
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>1236</v>
@@ -12790,7 +12875,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>1</v>
@@ -12799,12 +12884,12 @@
         <v>105</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>1228</v>
@@ -12822,24 +12907,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>105</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>1228</v>
@@ -12857,10 +12942,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>1</v>
@@ -12869,12 +12954,12 @@
         <v>110</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>1278</v>
@@ -12895,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>1</v>
@@ -12909,7 +12994,7 @@
     </row>
     <row r="12" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>1278</v>
@@ -12921,30 +13006,30 @@
         <v>392</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>113</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>1278</v>
@@ -12959,13 +13044,13 @@
         <v>1302</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>1</v>
@@ -12979,7 +13064,7 @@
     </row>
     <row r="14" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>1228</v>
@@ -12997,13 +13082,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>113</v>
@@ -13014,7 +13099,7 @@
     </row>
     <row r="15" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>1228</v>
@@ -13032,10 +13117,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="I15" s="10" t="s">
         <v>1</v>
@@ -13081,33 +13166,33 @@
         <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="E2" s="10">
         <v>1</v>
@@ -13118,16 +13203,16 @@
     </row>
     <row r="3" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="E3" s="10">
         <v>2</v>
@@ -13138,16 +13223,16 @@
     </row>
     <row r="4" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>1236</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="E4" s="10">
         <v>1</v>
@@ -13158,16 +13243,16 @@
     </row>
     <row r="5" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>1236</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="E5" s="10">
         <v>2</v>
@@ -13178,16 +13263,16 @@
     </row>
     <row r="6" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>1236</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="E6" s="10">
         <v>3</v>
@@ -13198,16 +13283,16 @@
     </row>
     <row r="7" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>1278</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="E7" s="10">
         <v>1</v>
@@ -13218,16 +13303,16 @@
     </row>
     <row r="8" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>1278</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E8" s="10">
         <v>2</v>
@@ -13238,16 +13323,16 @@
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="E9" s="10">
         <v>1</v>
@@ -13258,16 +13343,16 @@
     </row>
     <row r="10" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="E10" s="10">
         <v>2</v>
@@ -13278,16 +13363,16 @@
     </row>
     <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="E11" s="10">
         <v>3</v>
@@ -13298,16 +13383,16 @@
     </row>
     <row r="12" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="E12" s="10">
         <v>1</v>
@@ -13318,16 +13403,16 @@
     </row>
     <row r="13" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="E13" s="10">
         <v>2</v>
@@ -13338,16 +13423,16 @@
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="E14" s="10">
         <v>1</v>
@@ -13358,16 +13443,16 @@
     </row>
     <row r="15" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="E15" s="10">
         <v>2</v>
@@ -13378,16 +13463,16 @@
     </row>
     <row r="16" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>1228</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="E16" s="10">
         <v>1</v>
@@ -13398,16 +13483,16 @@
     </row>
     <row r="17" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>1228</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="E17" s="10">
         <v>2</v>
@@ -13418,16 +13503,16 @@
     </row>
     <row r="18" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="E18" s="10">
         <v>2</v>
@@ -13438,16 +13523,16 @@
     </row>
     <row r="19" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="E19" s="10">
         <v>1</v>
@@ -13458,16 +13543,16 @@
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="E20" s="10">
         <v>0</v>
@@ -13478,16 +13563,16 @@
     </row>
     <row r="21" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="E21" s="10">
         <v>3</v>
@@ -13533,28 +13618,28 @@
         <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>1228</v>
@@ -13562,63 +13647,63 @@
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>1</v>
@@ -13626,48 +13711,48 @@
     </row>
     <row r="4" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>1228</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>1</v>
@@ -13676,13 +13761,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>1</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>1</v>
@@ -13690,31 +13775,31 @@
     </row>
     <row r="6" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>1228</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>1574</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>1572</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>1</v>
@@ -13722,16 +13807,16 @@
     </row>
     <row r="7" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>1228</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>1</v>
@@ -13740,13 +13825,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>1</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>1</v>
@@ -13784,739 +13869,739 @@
         <v>70</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>208</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C3" s="10" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>1592</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>1593</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="19" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="22" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="29" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="30" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="31" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="32" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="37" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
     </row>
   </sheetData>
